--- a/(枠)◯年度一式/家電請求書.xlsx
+++ b/(枠)◯年度一式/家電請求書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\Desktop\R８年度一式\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\ドキュメント\日報月報他\(枠)◯年度一式\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{534EC70D-3156-4110-A980-1091B151FBFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91097B0C-201C-404E-AB4E-8BEF04A8738B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="225" windowWidth="16350" windowHeight="15480" xr2:uid="{6D3F0DFB-1AB5-4F12-BAD3-DA7AC3FDF1AC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{6D3F0DFB-1AB5-4F12-BAD3-DA7AC3FDF1AC}"/>
   </bookViews>
   <sheets>
     <sheet name="10万未満" sheetId="11" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="52">
   <si>
     <t>納額通知書</t>
     <rPh sb="0" eb="1">
@@ -114,22 +114,6 @@
     <t>　上記</t>
     <rPh sb="1" eb="3">
       <t>ジョウキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　　平成　　　年　　　月　　　日</t>
-    <rPh sb="2" eb="4">
-      <t>ヘイセイ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ツキ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>ニチ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -472,47 +456,63 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ベスト電器利尻店</t>
-  </si>
-  <si>
-    <t>　２月　　６日</t>
+    <t>\</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>㈲電器のオオミ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エアコン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テ レ ビ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>令和　9　年度</t>
+    <rPh sb="0" eb="2">
+      <t>レイワ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベスト電器</t>
+  </si>
+  <si>
+    <t>　　令和　　9　年　　4　月　　20　日</t>
+    <rPh sb="2" eb="4">
+      <t>レイワ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>住　吉　直　人</t>
+    <rPh sb="0" eb="1">
+      <t>ジュウ</t>
+    </rPh>
     <rPh sb="2" eb="3">
-      <t>ガツ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ニチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>\</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>㈲電器のオオミ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エアコン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>テ レ ビ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>電器のオオミ</t>
-  </si>
-  <si>
-    <t>熊　谷　洋　人</t>
-    <rPh sb="0" eb="1">
-      <t>クマ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>タニ</t>
+      <t>キチ</t>
     </rPh>
     <rPh sb="4" eb="5">
-      <t>ヨウ</t>
+      <t>チョク</t>
     </rPh>
     <rPh sb="6" eb="7">
       <t>ヒト</t>
@@ -520,47 +520,53 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>令和　　年度</t>
+    <t>令和9年</t>
     <rPh sb="0" eb="2">
       <t>レイワ</t>
     </rPh>
-    <rPh sb="4" eb="5">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>令和　年</t>
-    <rPh sb="0" eb="2">
-      <t>レイワ</t>
-    </rPh>
     <rPh sb="3" eb="4">
       <t>トシ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>令和　年度</t>
-    <rPh sb="0" eb="2">
+    <t>　4　月  20 日</t>
+    <rPh sb="3" eb="4">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　　令和　　　年　　　月　　　日</t>
+    <rPh sb="2" eb="4">
       <t>レイワ</t>
     </rPh>
-    <rPh sb="3" eb="4">
+    <rPh sb="7" eb="8">
       <t>ネン</t>
     </rPh>
-    <rPh sb="4" eb="5">
-      <t>ド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>　月　 日</t>
-    <rPh sb="1" eb="2">
-      <t>ガツ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
+    <rPh sb="11" eb="12">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　　令和　　　年　　　月　　　日</t>
+    <rPh sb="2" eb="4">
+      <t>レ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ツキ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
       <t>ニチ</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -571,13 +577,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
-    <numFmt numFmtId="179" formatCode="#,##0_);\(#,##0\)"/>
-    <numFmt numFmtId="181" formatCode="#,##0_ "/>
-    <numFmt numFmtId="182" formatCode="0_ "/>
-    <numFmt numFmtId="183" formatCode="0;[Red]0"/>
-    <numFmt numFmtId="187" formatCode="0;&quot;▲ &quot;0"/>
-    <numFmt numFmtId="188" formatCode="0_);\(0\)"/>
-    <numFmt numFmtId="189" formatCode="0;&quot;△ &quot;0"/>
+    <numFmt numFmtId="176" formatCode="#,##0_);\(#,##0\)"/>
+    <numFmt numFmtId="177" formatCode="#,##0_ "/>
+    <numFmt numFmtId="178" formatCode="0_ "/>
+    <numFmt numFmtId="179" formatCode="0;[Red]0"/>
+    <numFmt numFmtId="180" formatCode="0;&quot;▲ &quot;0"/>
+    <numFmt numFmtId="181" formatCode="0_);\(0\)"/>
+    <numFmt numFmtId="182" formatCode="0;&quot;△ &quot;0"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -1039,7 +1045,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1102,13 +1108,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1143,8 +1149,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="189" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1152,55 +1167,46 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="distributed"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="188" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="183" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1215,34 +1221,40 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" justifyLastLine="1"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" justifyLastLine="1"/>
     </xf>
-    <xf numFmtId="183" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
     </xf>
-    <xf numFmtId="183" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1261,10 +1273,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="12" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1284,10 +1296,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" justifyLastLine="1"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" justifyLastLine="1"/>
     </xf>
   </cellXfs>
@@ -1694,20 +1706,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
       <c r="I1" s="1"/>
       <c r="J1" s="36"/>
-      <c r="M1" s="54" t="s">
+      <c r="M1" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I2" s="1"/>
@@ -1734,12 +1746,14 @@
       <c r="R3" s="4"/>
     </row>
     <row r="4" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="71" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="88" t="s">
+      <c r="A4" s="73" t="s">
         <v>31</v>
+      </c>
+      <c r="B4" s="75">
+        <v>128</v>
+      </c>
+      <c r="C4" s="90" t="s">
+        <v>30</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>1</v>
@@ -1750,15 +1764,15 @@
       <c r="H4" s="6"/>
       <c r="I4" s="1"/>
       <c r="J4" s="36"/>
-      <c r="K4" s="71" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" s="73">
+      <c r="K4" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="75">
         <f>B4</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="88" t="s">
-        <v>31</v>
+        <v>128</v>
+      </c>
+      <c r="M4" s="90" t="s">
+        <v>30</v>
       </c>
       <c r="N4" s="16" t="s">
         <v>1</v>
@@ -1769,9 +1783,9 @@
       <c r="R4" s="6"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="72"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="89"/>
+      <c r="A5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="91"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -1779,9 +1793,9 @@
       <c r="H5" s="6"/>
       <c r="I5" s="1"/>
       <c r="J5" s="36"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="89"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="91"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
@@ -1789,75 +1803,75 @@
       <c r="R5" s="6"/>
     </row>
     <row r="6" spans="1:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="77" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="78"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="80" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
+      <c r="A6" s="79" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="80"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
       <c r="H6" s="14" t="s">
         <v>2</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="36"/>
-      <c r="K6" s="77" t="str">
+      <c r="K6" s="79" t="str">
         <f>A6</f>
-        <v>令和　年度</v>
-      </c>
-      <c r="L6" s="78"/>
-      <c r="M6" s="79"/>
-      <c r="N6" s="86" t="str">
+        <v>令和　9　年度</v>
+      </c>
+      <c r="L6" s="80"/>
+      <c r="M6" s="81"/>
+      <c r="N6" s="88" t="str">
         <f>IF(D6="","",D6)</f>
-        <v>電器のオオミ</v>
-      </c>
-      <c r="O6" s="87"/>
-      <c r="P6" s="87"/>
-      <c r="Q6" s="87"/>
+        <v>ベスト電器</v>
+      </c>
+      <c r="O6" s="89"/>
+      <c r="P6" s="89"/>
+      <c r="Q6" s="89"/>
       <c r="R6" s="14" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="82" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="84" t="s">
+      <c r="A7" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="85"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="87"/>
       <c r="I7" s="1"/>
       <c r="J7" s="36"/>
-      <c r="K7" s="82" t="s">
-        <v>14</v>
-      </c>
-      <c r="L7" s="83"/>
-      <c r="M7" s="84" t="s">
+      <c r="K7" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="N7" s="78"/>
-      <c r="O7" s="78"/>
-      <c r="P7" s="78"/>
-      <c r="Q7" s="78"/>
-      <c r="R7" s="85"/>
+      <c r="L7" s="85"/>
+      <c r="M7" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="N7" s="80"/>
+      <c r="O7" s="80"/>
+      <c r="P7" s="80"/>
+      <c r="Q7" s="80"/>
+      <c r="R7" s="87"/>
     </row>
     <row r="8" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="77" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>7</v>
@@ -1873,13 +1887,13 @@
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="36"/>
-      <c r="K8" s="75" t="s">
+      <c r="K8" s="77" t="s">
         <v>3</v>
       </c>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
       <c r="N8" s="31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O8" s="12" t="s">
         <v>7</v>
@@ -1895,10 +1909,10 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="76"/>
+      <c r="A9" s="78"/>
       <c r="B9" s="11"/>
       <c r="C9" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" s="18" t="str">
         <f>IF(G33="","",IF(ROUNDDOWN(G33/10000,0)=0,"",ROUNDDOWN(G33/10000,0)))</f>
@@ -1919,10 +1933,10 @@
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="36"/>
-      <c r="K9" s="76"/>
+      <c r="K9" s="78"/>
       <c r="L9" s="11"/>
       <c r="M9" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N9" s="18" t="str">
         <f>IF(D9="","",D9)</f>
@@ -1971,10 +1985,10 @@
       </c>
       <c r="B11" s="63"/>
       <c r="C11" s="41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -2013,7 +2027,7 @@
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" s="63"/>
       <c r="C13" s="63"/>
@@ -2025,7 +2039,7 @@
       <c r="I13" s="2"/>
       <c r="J13" s="36"/>
       <c r="K13" s="62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L13" s="63"/>
       <c r="M13" s="63"/>
@@ -2056,20 +2070,20 @@
       <c r="R14" s="6"/>
     </row>
     <row r="15" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="67"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="67"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="70"/>
+      <c r="A15" s="70" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="71"/>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="72"/>
       <c r="I15" s="2"/>
       <c r="J15" s="36"/>
-      <c r="K15" s="69" t="s">
-        <v>10</v>
+      <c r="K15" s="70" t="s">
+        <v>50</v>
       </c>
       <c r="L15" s="67"/>
       <c r="M15" s="67"/>
@@ -2077,7 +2091,7 @@
       <c r="O15" s="67"/>
       <c r="P15" s="67"/>
       <c r="Q15" s="67"/>
-      <c r="R15" s="70"/>
+      <c r="R15" s="72"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A16" s="8"/>
@@ -2121,7 +2135,7 @@
     </row>
     <row r="18" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -2133,7 +2147,7 @@
       <c r="I18" s="2"/>
       <c r="J18" s="36"/>
       <c r="K18" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
@@ -2146,28 +2160,28 @@
     <row r="19" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="8"/>
       <c r="B19" s="68" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="68"/>
       <c r="D19" s="68"/>
-      <c r="E19" s="65" t="s">
-        <v>40</v>
-      </c>
-      <c r="F19" s="65"/>
-      <c r="G19" s="65"/>
+      <c r="E19" s="69" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="69"/>
+      <c r="G19" s="69"/>
       <c r="H19" s="66"/>
       <c r="I19" s="2"/>
       <c r="J19" s="36"/>
       <c r="K19" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L19" s="67" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M19" s="67"/>
       <c r="N19" s="67"/>
       <c r="O19" s="65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P19" s="65"/>
       <c r="Q19" s="65"/>
@@ -2216,13 +2230,13 @@
     <row r="22" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1"/>
       <c r="B22" s="32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="32" t="s">
         <v>35</v>
-      </c>
-      <c r="D22" s="32" t="s">
-        <v>36</v>
       </c>
       <c r="E22" s="32"/>
       <c r="F22" s="1"/>
@@ -2240,107 +2254,107 @@
       <c r="R22" s="1"/>
     </row>
     <row r="23" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C23" s="54" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
+      <c r="C23" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
       <c r="I23" s="1"/>
       <c r="J23" s="36"/>
-      <c r="M23" s="54" t="s">
-        <v>18</v>
-      </c>
-      <c r="N23" s="54"/>
-      <c r="O23" s="54"/>
-      <c r="P23" s="54"/>
+      <c r="M23" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" s="56"/>
+      <c r="O23" s="56"/>
+      <c r="P23" s="56"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I24" s="1"/>
       <c r="J24" s="36"/>
     </row>
     <row r="25" spans="1:18" s="20" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="57" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" s="58"/>
-      <c r="C25" s="56" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="56"/>
-      <c r="E25" s="56"/>
+      <c r="A25" s="59" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="60"/>
+      <c r="C25" s="58" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
       <c r="F25" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" s="59">
+        <v>18</v>
+      </c>
+      <c r="G25" s="54">
         <f>B4</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="60"/>
+        <v>128</v>
+      </c>
+      <c r="H25" s="55"/>
       <c r="I25" s="17"/>
       <c r="J25" s="38"/>
-      <c r="K25" s="57" t="str">
+      <c r="K25" s="59" t="str">
         <f>A25</f>
-        <v>令和　年</v>
-      </c>
-      <c r="L25" s="58"/>
-      <c r="M25" s="56" t="str">
+        <v>令和9年</v>
+      </c>
+      <c r="L25" s="60"/>
+      <c r="M25" s="58" t="str">
         <f>C25</f>
-        <v>　月　 日</v>
-      </c>
-      <c r="N25" s="56"/>
-      <c r="O25" s="56"/>
+        <v>　4　月  20 日</v>
+      </c>
+      <c r="N25" s="58"/>
+      <c r="O25" s="58"/>
       <c r="P25" s="40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q25" s="61">
         <f>G25</f>
-        <v>0</v>
-      </c>
-      <c r="R25" s="60"/>
+        <v>128</v>
+      </c>
+      <c r="R25" s="55"/>
     </row>
     <row r="26" spans="1:18" s="20" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="46" t="s">
+      <c r="A26" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="43"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="44"/>
+      <c r="F26" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="46" t="s">
+      <c r="G26" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="E26" s="48"/>
-      <c r="F26" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="H26" s="48"/>
+      <c r="H26" s="44"/>
       <c r="I26" s="17"/>
       <c r="J26" s="38"/>
-      <c r="K26" s="46" t="s">
+      <c r="K26" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="L26" s="43"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="O26" s="44"/>
+      <c r="P26" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="L26" s="47"/>
-      <c r="M26" s="55"/>
-      <c r="N26" s="46" t="s">
+      <c r="Q26" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="O26" s="48"/>
-      <c r="P26" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q26" s="46" t="s">
+      <c r="R26" s="44"/>
+    </row>
+    <row r="27" spans="1:18" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="R26" s="48"/>
-    </row>
-    <row r="27" spans="1:18" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="47"/>
-      <c r="C27" s="48"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="44"/>
       <c r="D27" s="49">
         <v>2000</v>
       </c>
@@ -2353,11 +2367,11 @@
       <c r="H27" s="52"/>
       <c r="I27" s="17"/>
       <c r="J27" s="38"/>
-      <c r="K27" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="L27" s="47"/>
-      <c r="M27" s="48"/>
+      <c r="K27" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="43"/>
+      <c r="M27" s="44"/>
       <c r="N27" s="49">
         <v>2000</v>
       </c>
@@ -2373,11 +2387,11 @@
       <c r="R27" s="52"/>
     </row>
     <row r="28" spans="1:18" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="47"/>
-      <c r="C28" s="48"/>
+      <c r="A28" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="43"/>
+      <c r="C28" s="44"/>
       <c r="D28" s="49">
         <v>3000</v>
       </c>
@@ -2390,11 +2404,11 @@
       <c r="H28" s="52"/>
       <c r="I28" s="17"/>
       <c r="J28" s="38"/>
-      <c r="K28" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="L28" s="47"/>
-      <c r="M28" s="48"/>
+      <c r="K28" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" s="43"/>
+      <c r="M28" s="44"/>
       <c r="N28" s="49">
         <v>3000</v>
       </c>
@@ -2410,11 +2424,11 @@
       <c r="R28" s="52"/>
     </row>
     <row r="29" spans="1:18" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="47"/>
-      <c r="C29" s="48"/>
+      <c r="A29" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="43"/>
+      <c r="C29" s="44"/>
       <c r="D29" s="49">
         <v>3000</v>
       </c>
@@ -2427,11 +2441,11 @@
       <c r="H29" s="52"/>
       <c r="I29" s="17"/>
       <c r="J29" s="38"/>
-      <c r="K29" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="L29" s="47"/>
-      <c r="M29" s="48"/>
+      <c r="K29" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" s="43"/>
+      <c r="M29" s="44"/>
       <c r="N29" s="49">
         <v>3000</v>
       </c>
@@ -2447,11 +2461,11 @@
       <c r="R29" s="52"/>
     </row>
     <row r="30" spans="1:18" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="47"/>
-      <c r="C30" s="48"/>
+      <c r="A30" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="43"/>
+      <c r="C30" s="44"/>
       <c r="D30" s="49">
         <v>3000</v>
       </c>
@@ -2463,11 +2477,11 @@
       </c>
       <c r="H30" s="52"/>
       <c r="J30" s="38"/>
-      <c r="K30" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="L30" s="47"/>
-      <c r="M30" s="48"/>
+      <c r="K30" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="L30" s="43"/>
+      <c r="M30" s="44"/>
       <c r="N30" s="49">
         <v>3000</v>
       </c>
@@ -2483,11 +2497,11 @@
       <c r="R30" s="52"/>
     </row>
     <row r="31" spans="1:18" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="47"/>
-      <c r="C31" s="48"/>
+      <c r="A31" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="43"/>
+      <c r="C31" s="44"/>
       <c r="D31" s="49">
         <v>2000</v>
       </c>
@@ -2500,11 +2514,11 @@
       <c r="H31" s="52"/>
       <c r="I31" s="17"/>
       <c r="J31" s="38"/>
-      <c r="K31" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="L31" s="47"/>
-      <c r="M31" s="48"/>
+      <c r="K31" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="L31" s="43"/>
+      <c r="M31" s="44"/>
       <c r="N31" s="49">
         <v>2000</v>
       </c>
@@ -2521,10 +2535,10 @@
     </row>
     <row r="32" spans="1:18" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="47"/>
-      <c r="C32" s="48"/>
+        <v>32</v>
+      </c>
+      <c r="B32" s="43"/>
+      <c r="C32" s="44"/>
       <c r="D32" s="49">
         <v>2000</v>
       </c>
@@ -2538,10 +2552,10 @@
       <c r="I32" s="17"/>
       <c r="J32" s="38"/>
       <c r="K32" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="L32" s="47"/>
-      <c r="M32" s="48"/>
+        <v>32</v>
+      </c>
+      <c r="L32" s="43"/>
+      <c r="M32" s="44"/>
       <c r="N32" s="49">
         <v>2000</v>
       </c>
@@ -2557,40 +2571,40 @@
       <c r="R32" s="52"/>
     </row>
     <row r="33" spans="1:18" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="47"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="43"/>
+      <c r="A33" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" s="43"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="46"/>
       <c r="F33" s="23" t="str">
         <f>IF(SUM(F27:F32)=0,"",SUM(F27:F32))</f>
         <v/>
       </c>
-      <c r="G33" s="44" t="str">
+      <c r="G33" s="47" t="str">
         <f>IF(SUM(G27:H32)=0,"",SUM(G27:H32))</f>
         <v/>
       </c>
-      <c r="H33" s="45"/>
+      <c r="H33" s="48"/>
       <c r="I33" s="17"/>
       <c r="J33" s="38"/>
-      <c r="K33" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="L33" s="47"/>
-      <c r="M33" s="48"/>
-      <c r="N33" s="42"/>
-      <c r="O33" s="43"/>
+      <c r="K33" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="L33" s="43"/>
+      <c r="M33" s="44"/>
+      <c r="N33" s="45"/>
+      <c r="O33" s="46"/>
       <c r="P33" s="23" t="str">
         <f>IF(SUM(P27:P32)=0,"",SUM(P27:P32))</f>
         <v/>
       </c>
-      <c r="Q33" s="44" t="str">
+      <c r="Q33" s="47" t="str">
         <f>IF(SUM(Q27:R32)=0,"",SUM(Q27:R32))</f>
         <v/>
       </c>
-      <c r="R33" s="45"/>
+      <c r="R33" s="48"/>
     </row>
     <row r="34" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="1"/>
@@ -2631,8 +2645,6 @@
     </row>
   </sheetData>
   <mergeCells count="83">
-    <mergeCell ref="M7:R7"/>
-    <mergeCell ref="N6:Q6"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="M1:P1"/>
     <mergeCell ref="L4:L5"/>
@@ -2649,6 +2661,12 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:R7"/>
+    <mergeCell ref="N6:Q6"/>
+    <mergeCell ref="M23:P23"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="K26:M26"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="K13:R13"/>
@@ -2658,13 +2676,6 @@
     <mergeCell ref="E19:H19"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="K15:R15"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="M23:P23"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="K26:M26"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="D26:E26"/>
@@ -2682,46 +2693,49 @@
     <mergeCell ref="K27:M27"/>
     <mergeCell ref="G28:H28"/>
     <mergeCell ref="K28:M28"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="G30:H30"/>
     <mergeCell ref="N28:O28"/>
     <mergeCell ref="Q28:R28"/>
     <mergeCell ref="G31:H31"/>
     <mergeCell ref="K31:M31"/>
     <mergeCell ref="G29:H29"/>
     <mergeCell ref="K29:M29"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="G30:H30"/>
     <mergeCell ref="K30:M30"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="K32:M32"/>
     <mergeCell ref="N29:O29"/>
     <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="N31:O31"/>
     <mergeCell ref="Q31:R31"/>
     <mergeCell ref="N30:O30"/>
     <mergeCell ref="Q30:R30"/>
     <mergeCell ref="N33:O33"/>
     <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="Q32:R32"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="D33:E33"/>
     <mergeCell ref="G33:H33"/>
     <mergeCell ref="K33:M33"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="K32:M32"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="D31:E31"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
     <dataValidation type="decimal" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="自動計算されるので入力不可_x000a_" sqref="D9:H9" xr:uid="{3CB14B4E-A243-4650-9051-448582F1DEC8}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D6:G6" xr:uid="{E998CD9C-53D8-4E22-AFCF-E19201AD2753}">
-      <formula1>"ベスト電器利尻店,㈱洋　商,電器のオオミ,でんきのカトウ,㈲カワムラ電器,ツチヤ電気店,不二商会"</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="D6:G6" xr:uid="{7C28E655-DD1F-4CEF-9824-D1368FC26456}">
+      <formula1>"ベスト電器,㈲ヤマツ津田商店,㈲カワムラ電器,電器のオオミ"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -2748,20 +2762,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
       <c r="I1" s="1"/>
       <c r="J1" s="36"/>
-      <c r="M1" s="54" t="s">
+      <c r="M1" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I2" s="1"/>
@@ -2788,12 +2802,14 @@
       <c r="R3" s="4"/>
     </row>
     <row r="4" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="71" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="73"/>
-      <c r="C4" s="88" t="s">
+      <c r="A4" s="73" t="s">
         <v>31</v>
+      </c>
+      <c r="B4" s="75">
+        <v>128</v>
+      </c>
+      <c r="C4" s="90" t="s">
+        <v>30</v>
       </c>
       <c r="D4" s="16" t="s">
         <v>1</v>
@@ -2804,15 +2820,15 @@
       <c r="H4" s="6"/>
       <c r="I4" s="1"/>
       <c r="J4" s="36"/>
-      <c r="K4" s="71" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" s="73">
+      <c r="K4" s="73" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="75">
         <f>B4</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="88" t="s">
-        <v>31</v>
+        <v>128</v>
+      </c>
+      <c r="M4" s="90" t="s">
+        <v>30</v>
       </c>
       <c r="N4" s="16" t="s">
         <v>1</v>
@@ -2823,9 +2839,9 @@
       <c r="R4" s="6"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="72"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="89"/>
+      <c r="A5" s="74"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="91"/>
       <c r="D5" s="5"/>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -2833,9 +2849,9 @@
       <c r="H5" s="6"/>
       <c r="I5" s="1"/>
       <c r="J5" s="36"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="89"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="91"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
@@ -2843,75 +2859,75 @@
       <c r="R5" s="6"/>
     </row>
     <row r="6" spans="1:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="77" t="s">
-        <v>49</v>
-      </c>
-      <c r="B6" s="78"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="80" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
+      <c r="A6" s="79" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="80"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="82" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
       <c r="H6" s="14" t="s">
         <v>2</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="36"/>
-      <c r="K6" s="77" t="str">
+      <c r="K6" s="79" t="str">
         <f>A6</f>
-        <v>令和　　年度</v>
-      </c>
-      <c r="L6" s="78"/>
-      <c r="M6" s="79"/>
-      <c r="N6" s="86" t="str">
+        <v>令和　9　年度</v>
+      </c>
+      <c r="L6" s="80"/>
+      <c r="M6" s="81"/>
+      <c r="N6" s="88" t="str">
         <f>IF(D6="","",D6)</f>
-        <v>ベスト電器利尻店</v>
-      </c>
-      <c r="O6" s="87"/>
-      <c r="P6" s="87"/>
-      <c r="Q6" s="87"/>
+        <v>ベスト電器</v>
+      </c>
+      <c r="O6" s="89"/>
+      <c r="P6" s="89"/>
+      <c r="Q6" s="89"/>
       <c r="R6" s="14" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="82" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="84" t="s">
+      <c r="A7" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="85"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="80"/>
+      <c r="E7" s="80"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="87"/>
       <c r="I7" s="1"/>
       <c r="J7" s="36"/>
-      <c r="K7" s="82" t="s">
-        <v>14</v>
-      </c>
-      <c r="L7" s="83"/>
-      <c r="M7" s="84" t="s">
+      <c r="K7" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="N7" s="78"/>
-      <c r="O7" s="78"/>
-      <c r="P7" s="78"/>
-      <c r="Q7" s="78"/>
-      <c r="R7" s="85"/>
+      <c r="L7" s="85"/>
+      <c r="M7" s="86" t="s">
+        <v>12</v>
+      </c>
+      <c r="N7" s="80"/>
+      <c r="O7" s="80"/>
+      <c r="P7" s="80"/>
+      <c r="Q7" s="80"/>
+      <c r="R7" s="87"/>
     </row>
     <row r="8" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="77" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
       <c r="D8" s="31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>7</v>
@@ -2927,13 +2943,13 @@
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="36"/>
-      <c r="K8" s="75" t="s">
+      <c r="K8" s="77" t="s">
         <v>3</v>
       </c>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
       <c r="N8" s="31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O8" s="12" t="s">
         <v>7</v>
@@ -2949,9 +2965,9 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="76"/>
+      <c r="A9" s="78"/>
       <c r="B9" s="11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C9" s="18" t="str">
         <f>IF(G33="","",MOD(INT(G33/100000),10))</f>
@@ -2976,9 +2992,9 @@
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="36"/>
-      <c r="K9" s="76"/>
+      <c r="K9" s="78"/>
       <c r="L9" s="11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="M9" s="18" t="str">
         <f>IF(C9="","",C9)</f>
@@ -3031,10 +3047,10 @@
       </c>
       <c r="B11" s="63"/>
       <c r="C11" s="41">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
@@ -3073,7 +3089,7 @@
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="62" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" s="63"/>
       <c r="C13" s="63"/>
@@ -3085,7 +3101,7 @@
       <c r="I13" s="2"/>
       <c r="J13" s="36"/>
       <c r="K13" s="62" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L13" s="63"/>
       <c r="M13" s="63"/>
@@ -3116,20 +3132,20 @@
       <c r="R14" s="6"/>
     </row>
     <row r="15" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="69" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="67"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="67"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="70"/>
+      <c r="A15" s="70" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="71"/>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+      <c r="F15" s="71"/>
+      <c r="G15" s="71"/>
+      <c r="H15" s="72"/>
       <c r="I15" s="2"/>
       <c r="J15" s="36"/>
-      <c r="K15" s="69" t="s">
-        <v>10</v>
+      <c r="K15" s="70" t="s">
+        <v>51</v>
       </c>
       <c r="L15" s="67"/>
       <c r="M15" s="67"/>
@@ -3137,7 +3153,7 @@
       <c r="O15" s="67"/>
       <c r="P15" s="67"/>
       <c r="Q15" s="67"/>
-      <c r="R15" s="70"/>
+      <c r="R15" s="72"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A16" s="8"/>
@@ -3181,7 +3197,7 @@
     </row>
     <row r="18" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -3193,7 +3209,7 @@
       <c r="I18" s="2"/>
       <c r="J18" s="36"/>
       <c r="K18" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L18" s="5"/>
       <c r="M18" s="5"/>
@@ -3206,28 +3222,28 @@
     <row r="19" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="8"/>
       <c r="B19" s="68" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" s="68"/>
       <c r="D19" s="68"/>
-      <c r="E19" s="65" t="s">
-        <v>40</v>
-      </c>
-      <c r="F19" s="65"/>
-      <c r="G19" s="65"/>
+      <c r="E19" s="69" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="69"/>
+      <c r="G19" s="69"/>
       <c r="H19" s="66"/>
       <c r="I19" s="2"/>
       <c r="J19" s="36"/>
       <c r="K19" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L19" s="67" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M19" s="67"/>
       <c r="N19" s="67"/>
       <c r="O19" s="65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="P19" s="65"/>
       <c r="Q19" s="65"/>
@@ -3276,13 +3292,13 @@
     <row r="22" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1"/>
       <c r="B22" s="32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22" s="32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D22" s="32" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E22" s="32"/>
       <c r="F22" s="1"/>
@@ -3300,107 +3316,107 @@
       <c r="R22" s="1"/>
     </row>
     <row r="23" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C23" s="54" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="54"/>
-      <c r="E23" s="54"/>
-      <c r="F23" s="54"/>
+      <c r="C23" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="56"/>
+      <c r="E23" s="56"/>
+      <c r="F23" s="56"/>
       <c r="I23" s="1"/>
       <c r="J23" s="36"/>
-      <c r="M23" s="54" t="s">
-        <v>18</v>
-      </c>
-      <c r="N23" s="54"/>
-      <c r="O23" s="54"/>
-      <c r="P23" s="54"/>
+      <c r="M23" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" s="56"/>
+      <c r="O23" s="56"/>
+      <c r="P23" s="56"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.15">
       <c r="I24" s="1"/>
       <c r="J24" s="36"/>
     </row>
     <row r="25" spans="1:18" s="20" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="57" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" s="58"/>
-      <c r="C25" s="56" t="s">
-        <v>42</v>
-      </c>
-      <c r="D25" s="56"/>
-      <c r="E25" s="56"/>
+      <c r="A25" s="59" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="60"/>
+      <c r="C25" s="58" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
       <c r="F25" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" s="59">
+        <v>18</v>
+      </c>
+      <c r="G25" s="54">
         <f>B4</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="60"/>
+        <v>128</v>
+      </c>
+      <c r="H25" s="55"/>
       <c r="I25" s="17"/>
       <c r="J25" s="38"/>
-      <c r="K25" s="57" t="str">
+      <c r="K25" s="59" t="str">
         <f>A25</f>
-        <v>令和　年</v>
-      </c>
-      <c r="L25" s="58"/>
-      <c r="M25" s="56" t="str">
+        <v>令和9年</v>
+      </c>
+      <c r="L25" s="60"/>
+      <c r="M25" s="58" t="str">
         <f>C25</f>
-        <v>　２月　　６日</v>
-      </c>
-      <c r="N25" s="56"/>
-      <c r="O25" s="56"/>
+        <v>　4　月  20 日</v>
+      </c>
+      <c r="N25" s="58"/>
+      <c r="O25" s="58"/>
       <c r="P25" s="40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q25" s="61">
         <f>G25</f>
-        <v>0</v>
-      </c>
-      <c r="R25" s="60"/>
+        <v>128</v>
+      </c>
+      <c r="R25" s="55"/>
     </row>
     <row r="26" spans="1:18" s="20" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="46" t="s">
+      <c r="A26" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="43"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="44"/>
+      <c r="F26" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="47"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="46" t="s">
+      <c r="G26" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="E26" s="48"/>
-      <c r="F26" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="H26" s="48"/>
+      <c r="H26" s="44"/>
       <c r="I26" s="17"/>
       <c r="J26" s="38"/>
-      <c r="K26" s="46" t="s">
+      <c r="K26" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="L26" s="43"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="O26" s="44"/>
+      <c r="P26" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="L26" s="47"/>
-      <c r="M26" s="55"/>
-      <c r="N26" s="46" t="s">
+      <c r="Q26" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="O26" s="48"/>
-      <c r="P26" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q26" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="R26" s="48"/>
+      <c r="R26" s="44"/>
     </row>
     <row r="27" spans="1:18" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="47"/>
-      <c r="C27" s="48"/>
+      <c r="A27" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="43"/>
+      <c r="C27" s="44"/>
       <c r="D27" s="49">
         <v>2000</v>
       </c>
@@ -3413,11 +3429,11 @@
       <c r="H27" s="52"/>
       <c r="I27" s="17"/>
       <c r="J27" s="38"/>
-      <c r="K27" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="L27" s="47"/>
-      <c r="M27" s="48"/>
+      <c r="K27" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="L27" s="43"/>
+      <c r="M27" s="44"/>
       <c r="N27" s="49">
         <v>2000</v>
       </c>
@@ -3433,11 +3449,11 @@
       <c r="R27" s="52"/>
     </row>
     <row r="28" spans="1:18" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" s="47"/>
-      <c r="C28" s="48"/>
+      <c r="A28" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="43"/>
+      <c r="C28" s="44"/>
       <c r="D28" s="49">
         <v>3000</v>
       </c>
@@ -3450,11 +3466,11 @@
       <c r="H28" s="52"/>
       <c r="I28" s="17"/>
       <c r="J28" s="38"/>
-      <c r="K28" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="L28" s="47"/>
-      <c r="M28" s="48"/>
+      <c r="K28" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="L28" s="43"/>
+      <c r="M28" s="44"/>
       <c r="N28" s="49">
         <v>3000</v>
       </c>
@@ -3470,11 +3486,11 @@
       <c r="R28" s="52"/>
     </row>
     <row r="29" spans="1:18" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="47"/>
-      <c r="C29" s="48"/>
+      <c r="A29" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="43"/>
+      <c r="C29" s="44"/>
       <c r="D29" s="49">
         <v>3000</v>
       </c>
@@ -3487,11 +3503,11 @@
       <c r="H29" s="52"/>
       <c r="I29" s="17"/>
       <c r="J29" s="38"/>
-      <c r="K29" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="L29" s="47"/>
-      <c r="M29" s="48"/>
+      <c r="K29" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" s="43"/>
+      <c r="M29" s="44"/>
       <c r="N29" s="49">
         <v>3000</v>
       </c>
@@ -3507,11 +3523,11 @@
       <c r="R29" s="52"/>
     </row>
     <row r="30" spans="1:18" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="47"/>
-      <c r="C30" s="48"/>
+      <c r="A30" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="43"/>
+      <c r="C30" s="44"/>
       <c r="D30" s="49">
         <v>3000</v>
       </c>
@@ -3523,11 +3539,11 @@
       </c>
       <c r="H30" s="52"/>
       <c r="J30" s="38"/>
-      <c r="K30" s="46" t="s">
-        <v>34</v>
-      </c>
-      <c r="L30" s="47"/>
-      <c r="M30" s="48"/>
+      <c r="K30" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="L30" s="43"/>
+      <c r="M30" s="44"/>
       <c r="N30" s="49">
         <v>3000</v>
       </c>
@@ -3543,11 +3559,11 @@
       <c r="R30" s="52"/>
     </row>
     <row r="31" spans="1:18" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="B31" s="47"/>
-      <c r="C31" s="48"/>
+      <c r="A31" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="43"/>
+      <c r="C31" s="44"/>
       <c r="D31" s="49">
         <v>2000</v>
       </c>
@@ -3560,11 +3576,11 @@
       <c r="H31" s="52"/>
       <c r="I31" s="17"/>
       <c r="J31" s="38"/>
-      <c r="K31" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="L31" s="47"/>
-      <c r="M31" s="48"/>
+      <c r="K31" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="L31" s="43"/>
+      <c r="M31" s="44"/>
       <c r="N31" s="49">
         <v>2000</v>
       </c>
@@ -3581,10 +3597,10 @@
     </row>
     <row r="32" spans="1:18" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="B32" s="47"/>
-      <c r="C32" s="48"/>
+        <v>32</v>
+      </c>
+      <c r="B32" s="43"/>
+      <c r="C32" s="44"/>
       <c r="D32" s="49">
         <v>2000</v>
       </c>
@@ -3598,10 +3614,10 @@
       <c r="I32" s="17"/>
       <c r="J32" s="38"/>
       <c r="K32" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="L32" s="47"/>
-      <c r="M32" s="48"/>
+        <v>32</v>
+      </c>
+      <c r="L32" s="43"/>
+      <c r="M32" s="44"/>
       <c r="N32" s="49">
         <v>2000</v>
       </c>
@@ -3617,40 +3633,40 @@
       <c r="R32" s="52"/>
     </row>
     <row r="33" spans="1:18" s="20" customFormat="1" ht="39.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="47"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="43"/>
+      <c r="A33" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" s="43"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="45"/>
+      <c r="E33" s="46"/>
       <c r="F33" s="23" t="str">
         <f>IF(SUM(F27:F32)=0,"",SUM(F27:F32))</f>
         <v/>
       </c>
-      <c r="G33" s="44" t="str">
+      <c r="G33" s="47" t="str">
         <f>IF(SUM(G27:H32)=0,"",SUM(G27:H32))</f>
         <v/>
       </c>
-      <c r="H33" s="45"/>
+      <c r="H33" s="48"/>
       <c r="I33" s="17"/>
       <c r="J33" s="38"/>
-      <c r="K33" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="L33" s="47"/>
-      <c r="M33" s="48"/>
-      <c r="N33" s="42"/>
-      <c r="O33" s="43"/>
+      <c r="K33" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="L33" s="43"/>
+      <c r="M33" s="44"/>
+      <c r="N33" s="45"/>
+      <c r="O33" s="46"/>
       <c r="P33" s="23" t="str">
         <f>IF(SUM(P27:P32)=0,"",SUM(P27:P32))</f>
         <v/>
       </c>
-      <c r="Q33" s="44" t="str">
+      <c r="Q33" s="47" t="str">
         <f>IF(SUM(Q27:R32)=0,"",SUM(Q27:R32))</f>
         <v/>
       </c>
-      <c r="R33" s="45"/>
+      <c r="R33" s="48"/>
     </row>
     <row r="34" spans="1:18" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="1"/>
@@ -3723,9 +3739,6 @@
     <mergeCell ref="K28:M28"/>
     <mergeCell ref="N29:O29"/>
     <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="N27:O27"/>
     <mergeCell ref="Q27:R27"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="D28:E28"/>
@@ -3733,14 +3746,16 @@
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="G27:H27"/>
     <mergeCell ref="K27:M27"/>
-    <mergeCell ref="K26:M26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="N27:O27"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="D26:E26"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="G25:H25"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="Q26:R26"/>
     <mergeCell ref="M23:P23"/>
@@ -3751,6 +3766,12 @@
     <mergeCell ref="L19:N19"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="K25:L25"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="K15:R15"/>
+    <mergeCell ref="K26:M26"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="K8:K9"/>
     <mergeCell ref="A6:C6"/>
@@ -3758,16 +3779,11 @@
     <mergeCell ref="K6:M6"/>
     <mergeCell ref="M7:R7"/>
     <mergeCell ref="N6:Q6"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="M25:O25"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="M1:P1"/>
     <mergeCell ref="L4:L5"/>
     <mergeCell ref="M4:M5"/>
     <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="K15:R15"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="K4:K5"/>
@@ -3780,11 +3796,11 @@
     <dataValidation type="decimal" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="自動計算されるので入力不可_x000a_" sqref="F9:H9" xr:uid="{E80CDF56-0640-496D-8E9B-A0F8AB0CCD0B}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D6:G6" xr:uid="{11271B82-FAA3-4EB2-AA94-2A432B845340}">
-      <formula1>"ベスト電器利尻店,㈱洋　商,電器のオオミ,でんきのカトウ,㈲カワムラ電器,ツチヤ電気店,不二商会"</formula1>
-    </dataValidation>
     <dataValidation type="decimal" operator="lessThan" allowBlank="1" showInputMessage="1" error="自動計算されるので入力不可_x000a_" sqref="C9:E9" xr:uid="{3A968C2E-02FA-47DB-A012-673C50726111}">
       <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D6:G6" xr:uid="{8A8C9B4E-F5E2-4216-8C86-18CF4A7809CA}">
+      <formula1>"ベスト電器,㈲ヤマツ津田商店,㈲カワムラ電器,電器のオオミ"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
